--- a/tableau_synthese_corrige.xlsx
+++ b/tableau_synthese_corrige.xlsx
@@ -1408,7 +1408,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customFormat="1" customHeight="1" s="2">
+    <row r="8" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Réalisation en cours de formation
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H20" s="22" t="n"/>
     </row>
-    <row r="21" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="21" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de première année</t>
@@ -1928,7 +1928,7 @@
       <c r="G28" s="21" t="n"/>
       <c r="H28" s="22" t="n"/>
     </row>
-    <row r="29" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="29" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Réalisations en milieu professionnel en cours de seconde année</t>
@@ -2050,10 +2050,12 @@
       <c r="H37" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:H2"/>
